--- a/Data1.xlsx
+++ b/Data1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DATA PC INFRA\My Document\Baim Titip\Monitoring\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{236C6012-79F5-4B7F-90F6-C5A6B66A56C7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{941EE570-59E4-4D00-B7EE-DE23C562CB9F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8364" xr2:uid="{0B7CC9C1-C7D4-472C-99C5-3BAB89DB7F8B}"/>
   </bookViews>
@@ -27,6 +27,9 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
+    <t>Plan</t>
+  </si>
+  <si>
     <t>Jan</t>
   </si>
   <si>
@@ -66,13 +69,10 @@
     <t>Total</t>
   </si>
   <si>
-    <t>PLAN</t>
-  </si>
-  <si>
-    <t>AKTUAL</t>
-  </si>
-  <si>
-    <t>BULAN</t>
+    <t>Bulan</t>
+  </si>
+  <si>
+    <t>Aktual</t>
   </si>
 </sst>
 </file>
@@ -449,18 +449,18 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>15</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2" s="3">
         <v>456</v>
@@ -471,7 +471,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" s="3">
         <v>372</v>
@@ -482,7 +482,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" s="3">
         <v>535</v>
@@ -493,7 +493,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" s="3">
         <v>252</v>
@@ -504,7 +504,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" s="3">
         <v>504</v>
@@ -515,7 +515,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" s="3">
         <v>346</v>
@@ -526,7 +526,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" s="3">
         <v>429</v>
@@ -537,7 +537,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9" s="3">
         <v>276</v>
@@ -548,7 +548,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" s="3">
         <v>367</v>
@@ -559,7 +559,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11" s="3">
         <v>267</v>
@@ -570,7 +570,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B12" s="3">
         <v>217</v>
@@ -581,7 +581,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13" s="3">
         <v>217</v>
@@ -592,7 +592,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14" s="3">
         <v>342</v>

--- a/Data1.xlsx
+++ b/Data1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DATA PC INFRA\My Document\Baim Titip\Monitoring\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{941EE570-59E4-4D00-B7EE-DE23C562CB9F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3201449D-3CFF-450D-9609-0C1DF76B96A1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8364" xr2:uid="{0B7CC9C1-C7D4-472C-99C5-3BAB89DB7F8B}"/>
   </bookViews>
@@ -120,13 +120,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -448,13 +451,13 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>15</v>
       </c>
     </row>

--- a/Data1.xlsx
+++ b/Data1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DATA PC INFRA\My Document\Baim Titip\Monitoring\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3201449D-3CFF-450D-9609-0C1DF76B96A1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1458FE99-7D37-4684-9F9E-6E0699AB7035}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8364" xr2:uid="{0B7CC9C1-C7D4-472C-99C5-3BAB89DB7F8B}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="18">
   <si>
     <t>Plan</t>
   </si>
@@ -73,6 +73,12 @@
   </si>
   <si>
     <t>Aktual</t>
+  </si>
+  <si>
+    <t>FR Plan (L/Ton)</t>
+  </si>
+  <si>
+    <t>FR Aktual (L/Ton)</t>
   </si>
 </sst>
 </file>
@@ -120,7 +126,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -132,6 +138,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma 6 4 4 3" xfId="1" xr:uid="{8B33C0AD-E798-464F-A388-05BA828B0ECF}"/>
@@ -447,8 +454,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8B32756-FFC0-44E7-90C3-1F337A018DB5}">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="15" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
@@ -607,6 +617,186 @@
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B15" s="1"/>
     </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B18" s="5">
+        <v>0.03</v>
+      </c>
+      <c r="C18" s="5">
+        <v>0.03</v>
+      </c>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B19" s="5">
+        <v>0.03</v>
+      </c>
+      <c r="C19" s="5">
+        <v>0.03</v>
+      </c>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B20" s="5">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="C20" s="5">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" s="5">
+        <v>0.03</v>
+      </c>
+      <c r="C21" s="5">
+        <v>0.03</v>
+      </c>
+      <c r="F21" s="5"/>
+      <c r="G21" s="5"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B22" s="5">
+        <v>0.03</v>
+      </c>
+      <c r="C22" s="5">
+        <v>0.03</v>
+      </c>
+      <c r="F22" s="5"/>
+      <c r="G22" s="5"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B23" s="5">
+        <v>0.04</v>
+      </c>
+      <c r="C23" s="5">
+        <v>0.04</v>
+      </c>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B24" s="5">
+        <v>0.03</v>
+      </c>
+      <c r="C24" s="5">
+        <v>0.03</v>
+      </c>
+      <c r="F24" s="5"/>
+      <c r="G24" s="5"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" s="5">
+        <v>0.03</v>
+      </c>
+      <c r="C25" s="5">
+        <v>0.03</v>
+      </c>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" s="5">
+        <v>0.03</v>
+      </c>
+      <c r="C26" s="5">
+        <v>0.02</v>
+      </c>
+      <c r="F26" s="5"/>
+      <c r="G26" s="5"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B27" s="5">
+        <v>0.03</v>
+      </c>
+      <c r="C27" s="5">
+        <v>0.02</v>
+      </c>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B28" s="5">
+        <v>0.02</v>
+      </c>
+      <c r="C28" s="5">
+        <v>0</v>
+      </c>
+      <c r="F28" s="5"/>
+      <c r="G28" s="5"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B29" s="5">
+        <v>0.02</v>
+      </c>
+      <c r="C29" s="5">
+        <v>0</v>
+      </c>
+      <c r="F29" s="5"/>
+      <c r="G29" s="5"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B30" s="5">
+        <v>0.03</v>
+      </c>
+      <c r="C30" s="5">
+        <v>0.03</v>
+      </c>
+      <c r="F30" s="5"/>
+      <c r="G30" s="5"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Data1.xlsx
+++ b/Data1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DATA PC INFRA\My Document\Baim Titip\Monitoring\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1458FE99-7D37-4684-9F9E-6E0699AB7035}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{119B7C40-56EF-4DD2-B342-2D2BC5728E7A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8364" xr2:uid="{0B7CC9C1-C7D4-472C-99C5-3BAB89DB7F8B}"/>
   </bookViews>
@@ -460,7 +460,7 @@
     <col min="1" max="2" width="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>14</v>
       </c>
@@ -470,8 +470,17 @@
       <c r="C1" s="4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -481,8 +490,17 @@
       <c r="C2" s="3">
         <v>456</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="5">
+        <v>0.03</v>
+      </c>
+      <c r="G2" s="5">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -492,8 +510,17 @@
       <c r="C3" s="3">
         <v>372</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="5">
+        <v>0.03</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
@@ -503,8 +530,17 @@
       <c r="C4" s="3">
         <v>535</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="5">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="G4" s="5">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
@@ -514,8 +550,17 @@
       <c r="C5" s="3">
         <v>252</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F5" s="5">
+        <v>0.03</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
@@ -525,8 +570,17 @@
       <c r="C6" s="3">
         <v>504</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F6" s="5">
+        <v>0.03</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
@@ -536,8 +590,17 @@
       <c r="C7" s="3">
         <v>346</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F7" s="5">
+        <v>0.04</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
@@ -547,8 +610,17 @@
       <c r="C8" s="3">
         <v>169</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F8" s="5">
+        <v>0.03</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
@@ -558,8 +630,17 @@
       <c r="C9" s="3">
         <v>166</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" s="5">
+        <v>0.03</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
@@ -569,8 +650,17 @@
       <c r="C10" s="3">
         <v>426</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="5">
+        <v>0.03</v>
+      </c>
+      <c r="G10" s="5">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
@@ -580,8 +670,17 @@
       <c r="C11" s="3">
         <v>464</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" s="5">
+        <v>0.03</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
@@ -591,8 +690,17 @@
       <c r="C12" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E12" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="5">
+        <v>0.02</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
@@ -602,8 +710,17 @@
       <c r="C13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" s="5">
+        <v>0.02</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>13</v>
       </c>
@@ -613,187 +730,68 @@
       <c r="C14" s="3">
         <v>360</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="E14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F14" s="5">
+        <v>0.03</v>
+      </c>
+      <c r="G14" s="5">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B15" s="1"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B18" s="5">
-        <v>0.03</v>
-      </c>
-      <c r="C18" s="5">
-        <v>0.03</v>
-      </c>
+    <row r="18" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B19" s="5">
-        <v>0.03</v>
-      </c>
-      <c r="C19" s="5">
-        <v>0.03</v>
-      </c>
+    <row r="19" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B20" s="5">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="C20" s="5">
-        <v>7.0000000000000007E-2</v>
-      </c>
+    <row r="20" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B21" s="5">
-        <v>0.03</v>
-      </c>
-      <c r="C21" s="5">
-        <v>0.03</v>
-      </c>
+    <row r="21" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F21" s="5"/>
       <c r="G21" s="5"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B22" s="5">
-        <v>0.03</v>
-      </c>
-      <c r="C22" s="5">
-        <v>0.03</v>
-      </c>
+    <row r="22" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F22" s="5"/>
       <c r="G22" s="5"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B23" s="5">
-        <v>0.04</v>
-      </c>
-      <c r="C23" s="5">
-        <v>0.04</v>
-      </c>
+    <row r="23" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F23" s="5"/>
       <c r="G23" s="5"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B24" s="5">
-        <v>0.03</v>
-      </c>
-      <c r="C24" s="5">
-        <v>0.03</v>
-      </c>
+    <row r="24" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F24" s="5"/>
       <c r="G24" s="5"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B25" s="5">
-        <v>0.03</v>
-      </c>
-      <c r="C25" s="5">
-        <v>0.03</v>
-      </c>
+    <row r="25" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F25" s="5"/>
       <c r="G25" s="5"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B26" s="5">
-        <v>0.03</v>
-      </c>
-      <c r="C26" s="5">
-        <v>0.02</v>
-      </c>
+    <row r="26" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F26" s="5"/>
       <c r="G26" s="5"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B27" s="5">
-        <v>0.03</v>
-      </c>
-      <c r="C27" s="5">
-        <v>0.02</v>
-      </c>
+    <row r="27" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F27" s="5"/>
       <c r="G27" s="5"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B28" s="5">
-        <v>0.02</v>
-      </c>
-      <c r="C28" s="5">
-        <v>0</v>
-      </c>
+    <row r="28" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F28" s="5"/>
       <c r="G28" s="5"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B29" s="5">
-        <v>0.02</v>
-      </c>
-      <c r="C29" s="5">
-        <v>0</v>
-      </c>
+    <row r="29" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F29" s="5"/>
       <c r="G29" s="5"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A30" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B30" s="5">
-        <v>0.03</v>
-      </c>
-      <c r="C30" s="5">
-        <v>0.03</v>
-      </c>
+    <row r="30" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F30" s="5"/>
       <c r="G30" s="5"/>
     </row>

--- a/Data1.xlsx
+++ b/Data1.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DATA PC INFRA\My Document\Baim Titip\Monitoring\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{119B7C40-56EF-4DD2-B342-2D2BC5728E7A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4612316C-4B27-4CF5-846B-4E08EED915D3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8364" xr2:uid="{0B7CC9C1-C7D4-472C-99C5-3BAB89DB7F8B}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8364" activeTab="1" xr2:uid="{0B7CC9C1-C7D4-472C-99C5-3BAB89DB7F8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -460,7 +461,7 @@
     <col min="1" max="2" width="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>14</v>
       </c>
@@ -470,17 +471,8 @@
       <c r="C1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -490,17 +482,8 @@
       <c r="C2" s="3">
         <v>456</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2" s="5">
-        <v>0.03</v>
-      </c>
-      <c r="G2" s="5">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -510,17 +493,8 @@
       <c r="C3" s="3">
         <v>372</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" s="5">
-        <v>0.03</v>
-      </c>
-      <c r="G3" s="5">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
@@ -530,17 +504,8 @@
       <c r="C4" s="3">
         <v>535</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F4" s="5">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="G4" s="5">
-        <v>7.0000000000000007E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
@@ -550,17 +515,8 @@
       <c r="C5" s="3">
         <v>252</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F5" s="5">
-        <v>0.03</v>
-      </c>
-      <c r="G5" s="5">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
@@ -570,17 +526,8 @@
       <c r="C6" s="3">
         <v>504</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" s="5">
-        <v>0.03</v>
-      </c>
-      <c r="G6" s="5">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
@@ -590,17 +537,8 @@
       <c r="C7" s="3">
         <v>346</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F7" s="5">
-        <v>0.04</v>
-      </c>
-      <c r="G7" s="5">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
@@ -610,17 +548,8 @@
       <c r="C8" s="3">
         <v>169</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" s="5">
-        <v>0.03</v>
-      </c>
-      <c r="G8" s="5">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
@@ -630,17 +559,8 @@
       <c r="C9" s="3">
         <v>166</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" s="5">
-        <v>0.03</v>
-      </c>
-      <c r="G9" s="5">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
@@ -650,17 +570,8 @@
       <c r="C10" s="3">
         <v>426</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" s="5">
-        <v>0.03</v>
-      </c>
-      <c r="G10" s="5">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
@@ -670,17 +581,8 @@
       <c r="C11" s="3">
         <v>464</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" s="5">
-        <v>0.03</v>
-      </c>
-      <c r="G11" s="5">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
@@ -690,17 +592,8 @@
       <c r="C12" s="3">
         <v>0</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F12" s="5">
-        <v>0.02</v>
-      </c>
-      <c r="G12" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
@@ -710,17 +603,8 @@
       <c r="C13" s="3">
         <v>0</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F13" s="5">
-        <v>0.02</v>
-      </c>
-      <c r="G13" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>13</v>
       </c>
@@ -730,17 +614,8 @@
       <c r="C14" s="3">
         <v>360</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F14" s="5">
-        <v>0.03</v>
-      </c>
-      <c r="G14" s="5">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B15" s="1"/>
     </row>
     <row r="18" spans="6:7" x14ac:dyDescent="0.3">
@@ -794,6 +669,174 @@
     <row r="30" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F30" s="5"/>
       <c r="G30" s="5"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CB5B793-83ED-4D08-8874-A3F4B3680141}">
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5">
+        <v>0.03</v>
+      </c>
+      <c r="C2" s="5">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="5">
+        <v>0.03</v>
+      </c>
+      <c r="C3" s="5">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="C4" s="5">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5">
+        <v>0.03</v>
+      </c>
+      <c r="C5" s="5">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="5">
+        <v>0.03</v>
+      </c>
+      <c r="C6" s="5">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="5">
+        <v>0.04</v>
+      </c>
+      <c r="C7" s="5">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5">
+        <v>0.03</v>
+      </c>
+      <c r="C8" s="5">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5">
+        <v>0.03</v>
+      </c>
+      <c r="C9" s="5">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="5">
+        <v>0.03</v>
+      </c>
+      <c r="C10" s="5">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5">
+        <v>0.03</v>
+      </c>
+      <c r="C11" s="5">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="5">
+        <v>0.02</v>
+      </c>
+      <c r="C12" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="5">
+        <v>0.02</v>
+      </c>
+      <c r="C13" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="5">
+        <v>0.03</v>
+      </c>
+      <c r="C14" s="5">
+        <v>0.03</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Data1.xlsx
+++ b/Data1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DATA PC INFRA\My Document\Baim Titip\Monitoring\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4612316C-4B27-4CF5-846B-4E08EED915D3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2628654-0BF4-4B5B-99D1-310D031E1417}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8364" activeTab="1" xr2:uid="{0B7CC9C1-C7D4-472C-99C5-3BAB89DB7F8B}"/>
   </bookViews>
@@ -76,10 +76,10 @@
     <t>Aktual</t>
   </si>
   <si>
-    <t>FR Plan (L/Ton)</t>
-  </si>
-  <si>
-    <t>FR Aktual (L/Ton)</t>
+    <t>FR Plan</t>
+  </si>
+  <si>
+    <t>FR Aktual</t>
   </si>
 </sst>
 </file>

--- a/Data1.xlsx
+++ b/Data1.xlsx
@@ -8,13 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DATA PC INFRA\My Document\Baim Titip\Monitoring\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2628654-0BF4-4B5B-99D1-310D031E1417}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AE28A8C-3688-4907-8E7F-59635F104549}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8364" activeTab="1" xr2:uid="{0B7CC9C1-C7D4-472C-99C5-3BAB89DB7F8B}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8364" xr2:uid="{0B7CC9C1-C7D4-472C-99C5-3BAB89DB7F8B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -26,10 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="18">
-  <si>
-    <t>Plan</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>Jan</t>
   </si>
@@ -73,13 +69,16 @@
     <t>Bulan</t>
   </si>
   <si>
-    <t>Aktual</t>
-  </si>
-  <si>
-    <t>FR Plan</t>
-  </si>
-  <si>
-    <t>FR Aktual</t>
+    <t>Plan_Cost</t>
+  </si>
+  <si>
+    <t>Aktual_Cost</t>
+  </si>
+  <si>
+    <t>Plan_Fuel</t>
+  </si>
+  <si>
+    <t>Aktual_Fuel</t>
   </si>
 </sst>
 </file>
@@ -461,20 +460,26 @@
     <col min="1" max="2" width="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>14</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>0</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2" s="3">
         <v>456</v>
@@ -482,10 +487,16 @@
       <c r="C2" s="3">
         <v>456</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D2" s="5">
+        <v>0.03</v>
+      </c>
+      <c r="E2" s="5">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" s="3">
         <v>372</v>
@@ -493,10 +504,16 @@
       <c r="C3" s="3">
         <v>372</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D3" s="5">
+        <v>0.03</v>
+      </c>
+      <c r="E3" s="5">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" s="3">
         <v>535</v>
@@ -504,10 +521,16 @@
       <c r="C4" s="3">
         <v>535</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D4" s="5">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="E4" s="5">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="3">
         <v>252</v>
@@ -515,10 +538,16 @@
       <c r="C5" s="3">
         <v>252</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D5" s="5">
+        <v>0.03</v>
+      </c>
+      <c r="E5" s="5">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" s="3">
         <v>504</v>
@@ -526,10 +555,16 @@
       <c r="C6" s="3">
         <v>504</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D6" s="5">
+        <v>0.03</v>
+      </c>
+      <c r="E6" s="5">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B7" s="3">
         <v>346</v>
@@ -537,10 +572,16 @@
       <c r="C7" s="3">
         <v>346</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D7" s="5">
+        <v>0.04</v>
+      </c>
+      <c r="E7" s="5">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" s="3">
         <v>429</v>
@@ -548,10 +589,16 @@
       <c r="C8" s="3">
         <v>169</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D8" s="5">
+        <v>0.03</v>
+      </c>
+      <c r="E8" s="5">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" s="3">
         <v>276</v>
@@ -559,10 +606,16 @@
       <c r="C9" s="3">
         <v>166</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D9" s="5">
+        <v>0.03</v>
+      </c>
+      <c r="E9" s="5">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B10" s="3">
         <v>367</v>
@@ -570,10 +623,16 @@
       <c r="C10" s="3">
         <v>426</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D10" s="5">
+        <v>0.03</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B11" s="3">
         <v>267</v>
@@ -581,10 +640,16 @@
       <c r="C11" s="3">
         <v>464</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D11" s="5">
+        <v>0.03</v>
+      </c>
+      <c r="E11" s="5">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" s="3">
         <v>217</v>
@@ -592,10 +657,16 @@
       <c r="C12" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D12" s="5">
+        <v>0.02</v>
+      </c>
+      <c r="E12" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" s="3">
         <v>217</v>
@@ -603,10 +674,16 @@
       <c r="C13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D13" s="5">
+        <v>0.02</v>
+      </c>
+      <c r="E13" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" s="3">
         <v>342</v>
@@ -614,8 +691,14 @@
       <c r="C14" s="3">
         <v>360</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D14" s="5">
+        <v>0.03</v>
+      </c>
+      <c r="E14" s="5">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="B15" s="1"/>
     </row>
     <row r="18" spans="6:7" x14ac:dyDescent="0.3">
@@ -669,174 +752,6 @@
     <row r="30" spans="6:7" x14ac:dyDescent="0.3">
       <c r="F30" s="5"/>
       <c r="G30" s="5"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CB5B793-83ED-4D08-8874-A3F4B3680141}">
-  <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="5">
-        <v>0.03</v>
-      </c>
-      <c r="C2" s="5">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="5">
-        <v>0.03</v>
-      </c>
-      <c r="C3" s="5">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="5">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="C4" s="5">
-        <v>7.0000000000000007E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="5">
-        <v>0.03</v>
-      </c>
-      <c r="C5" s="5">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="5">
-        <v>0.03</v>
-      </c>
-      <c r="C6" s="5">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="5">
-        <v>0.04</v>
-      </c>
-      <c r="C7" s="5">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="5">
-        <v>0.03</v>
-      </c>
-      <c r="C8" s="5">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="5">
-        <v>0.03</v>
-      </c>
-      <c r="C9" s="5">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="5">
-        <v>0.03</v>
-      </c>
-      <c r="C10" s="5">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" s="5">
-        <v>0.03</v>
-      </c>
-      <c r="C11" s="5">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" s="5">
-        <v>0.02</v>
-      </c>
-      <c r="C12" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B13" s="5">
-        <v>0.02</v>
-      </c>
-      <c r="C13" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" s="5">
-        <v>0.03</v>
-      </c>
-      <c r="C14" s="5">
-        <v>0.03</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Data1.xlsx
+++ b/Data1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DATA PC INFRA\My Document\Baim Titip\Monitoring\Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AE28A8C-3688-4907-8E7F-59635F104549}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D430303-828D-43EB-BDBA-D57B3166EA32}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8364" xr2:uid="{0B7CC9C1-C7D4-472C-99C5-3BAB89DB7F8B}"/>
   </bookViews>
@@ -72,13 +72,13 @@
     <t>Plan_Cost</t>
   </si>
   <si>
-    <t>Aktual_Cost</t>
-  </si>
-  <si>
     <t>Plan_Fuel</t>
   </si>
   <si>
-    <t>Aktual_Fuel</t>
+    <t>Actual_Cost</t>
+  </si>
+  <si>
+    <t>Actual_Fuel</t>
   </si>
 </sst>
 </file>
@@ -468,10 +468,10 @@
         <v>14</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" t="s">
         <v>15</v>
-      </c>
-      <c r="D1" t="s">
-        <v>16</v>
       </c>
       <c r="E1" t="s">
         <v>17</v>
